--- a/xlsx/Power/p23.xlsx
+++ b/xlsx/Power/p23.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF1C1F6-E0E8-42BB-B9E0-040742F9D2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C68DB9-51A3-4E66-8737-FD1BA4E74E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E325A220-9FA4-40D5-B3CC-EDAAF5B26F1A}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E325A220-9FA4-40D5-B3CC-EDAAF5B26F1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.27500000000000002</v>
       </c>
       <c r="C1">
-        <v>0.39500000000000002</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D1">
-        <v>0.47399999999999998</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="E1">
-        <v>0.56599999999999995</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="F1">
-        <v>0.61899999999999999</v>
+        <v>0.502</v>
       </c>
       <c r="G1">
-        <v>0.68500000000000005</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="H1">
-        <v>0.73199999999999998</v>
+        <v>0.65400000000000003</v>
       </c>
       <c r="I1">
-        <v>0.78</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="J1">
-        <v>0.80100000000000005</v>
+        <v>0.74399999999999999</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.313</v>
       </c>
       <c r="C2">
-        <v>0.442</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="D2">
-        <v>0.53</v>
+        <v>0.312</v>
       </c>
       <c r="E2">
-        <v>0.60599999999999998</v>
+        <v>0.47399999999999998</v>
       </c>
       <c r="F2">
-        <v>0.66300000000000003</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="G2">
-        <v>0.72399999999999998</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="H2">
-        <v>0.77</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="I2">
-        <v>0.81299999999999994</v>
+        <v>0.76400000000000001</v>
       </c>
       <c r="J2">
-        <v>0.84599999999999997</v>
+        <v>0.79400000000000004</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.23599999999999999</v>
       </c>
       <c r="C3">
-        <v>0.32900000000000001</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="D3">
-        <v>0.40200000000000002</v>
+        <v>0.41</v>
       </c>
       <c r="E3">
-        <v>0.46899999999999997</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="F3">
-        <v>0.52500000000000002</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="G3">
-        <v>0.55400000000000005</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="H3">
         <v>0.59199999999999997</v>
       </c>
       <c r="I3">
-        <v>0.66500000000000004</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="J3">
-        <v>0.66900000000000004</v>
+        <v>0.67100000000000004</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.14299999999999999</v>
+        <v>0.157</v>
       </c>
       <c r="B4">
-        <v>0.19800000000000001</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="C4">
-        <v>0.29299999999999998</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="D4">
-        <v>0.36199999999999999</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="E4">
         <v>0.41799999999999998</v>
       </c>
       <c r="F4">
-        <v>0.47499999999999998</v>
+        <v>0.47699999999999998</v>
       </c>
       <c r="G4">
         <v>0.48599999999999999</v>
       </c>
       <c r="H4">
-        <v>0.52600000000000002</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="I4">
         <v>0.58499999999999996</v>
       </c>
       <c r="J4">
-        <v>0.59499999999999997</v>
+        <v>0.59799999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="C5">
-        <v>6.4000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>6.9000000000000006E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="E5">
-        <v>7.0999999999999994E-2</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="F5">
-        <v>6.0999999999999999E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G5">
-        <v>6.3E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="H5">
-        <v>7.0000000000000007E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="I5">
-        <v>6.8000000000000005E-2</v>
+        <v>0.02</v>
       </c>
       <c r="J5">
-        <v>5.6000000000000001E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.33800000000000002</v>
       </c>
       <c r="C6">
-        <v>0.46500000000000002</v>
+        <v>0.55200000000000005</v>
       </c>
       <c r="D6">
-        <v>0.55400000000000005</v>
+        <v>0.59399999999999997</v>
       </c>
       <c r="E6">
-        <v>0.625</v>
+        <v>0.64</v>
       </c>
       <c r="F6">
-        <v>0.69</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="G6">
-        <v>0.75700000000000001</v>
+        <v>0.75900000000000001</v>
       </c>
       <c r="H6">
-        <v>0.78900000000000003</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="I6">
-        <v>0.83299999999999996</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="J6">
-        <v>0.86199999999999999</v>
+        <v>0.86599999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,7 +596,7 @@
         <v>0.33</v>
       </c>
       <c r="C7">
-        <v>0.45100000000000001</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="D7">
         <v>0.51500000000000001</v>
@@ -608,7 +608,7 @@
         <v>0.65700000000000003</v>
       </c>
       <c r="G7">
-        <v>0.72399999999999998</v>
+        <v>0.72099999999999997</v>
       </c>
       <c r="H7">
         <v>0.76700000000000002</v>
@@ -628,28 +628,28 @@
         <v>0.129</v>
       </c>
       <c r="C8">
-        <v>0.20799999999999999</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.24099999999999999</v>
+        <v>5.5E-2</v>
       </c>
       <c r="E8">
-        <v>0.29799999999999999</v>
+        <v>0.127</v>
       </c>
       <c r="F8">
-        <v>0.32200000000000001</v>
+        <v>0.187</v>
       </c>
       <c r="G8">
-        <v>0.36399999999999999</v>
+        <v>0.247</v>
       </c>
       <c r="H8">
-        <v>0.42799999999999999</v>
+        <v>0.32100000000000001</v>
       </c>
       <c r="I8">
-        <v>0.47899999999999998</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="J8">
-        <v>0.5</v>
+        <v>0.16800000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="C9">
-        <v>0.28899999999999998</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="D9">
-        <v>0.17</v>
+        <v>0.85899999999999999</v>
       </c>
       <c r="E9">
-        <v>0.17299999999999999</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="F9">
-        <v>0.14699999999999999</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="G9">
-        <v>0.14099999999999999</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="H9">
-        <v>0.16500000000000001</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="I9">
-        <v>0.185</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="J9">
-        <v>0.184</v>
+        <v>0.20599999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p23.xlsx
+++ b/xlsx/Power/p23.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C68DB9-51A3-4E66-8737-FD1BA4E74E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A5B4EE-0023-4B65-832E-9FFA63ABA364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E325A220-9FA4-40D5-B3CC-EDAAF5B26F1A}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E325A220-9FA4-40D5-B3CC-EDAAF5B26F1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,34 +398,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.152</v>
+        <v>0.153</v>
       </c>
       <c r="B1">
         <v>0.27500000000000002</v>
       </c>
       <c r="C1">
-        <v>0.14000000000000001</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="D1">
-        <v>0.26900000000000002</v>
+        <v>0.47399999999999998</v>
       </c>
       <c r="E1">
-        <v>0.41499999999999998</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="F1">
-        <v>0.502</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="G1">
-        <v>0.57399999999999995</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H1">
-        <v>0.65400000000000003</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="I1">
-        <v>0.72199999999999998</v>
+        <v>0.78</v>
       </c>
       <c r="J1">
-        <v>0.74399999999999999</v>
+        <v>0.80100000000000005</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.313</v>
       </c>
       <c r="C2">
-        <v>0.17899999999999999</v>
+        <v>0.442</v>
       </c>
       <c r="D2">
-        <v>0.312</v>
+        <v>0.53</v>
       </c>
       <c r="E2">
-        <v>0.47399999999999998</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="F2">
-        <v>0.55400000000000005</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="G2">
-        <v>0.63900000000000001</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="H2">
-        <v>0.70699999999999996</v>
+        <v>0.77</v>
       </c>
       <c r="I2">
-        <v>0.76400000000000001</v>
+        <v>0.81299999999999994</v>
       </c>
       <c r="J2">
-        <v>0.79400000000000004</v>
+        <v>0.84599999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.23599999999999999</v>
       </c>
       <c r="C3">
-        <v>0.36699999999999999</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="D3">
-        <v>0.41</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="E3">
-        <v>0.47799999999999998</v>
+        <v>0.46899999999999997</v>
       </c>
       <c r="F3">
-        <v>0.53100000000000003</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="G3">
-        <v>0.55600000000000005</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="H3">
         <v>0.59199999999999997</v>
       </c>
       <c r="I3">
-        <v>0.66700000000000004</v>
+        <v>0.66500000000000004</v>
       </c>
       <c r="J3">
-        <v>0.67100000000000004</v>
+        <v>0.66900000000000004</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.157</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="B4">
-        <v>0.20100000000000001</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="C4">
-        <v>0.29899999999999999</v>
+        <v>0.29299999999999998</v>
       </c>
       <c r="D4">
-        <v>0.36099999999999999</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="E4">
         <v>0.41799999999999998</v>
       </c>
       <c r="F4">
-        <v>0.47699999999999998</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="G4">
         <v>0.48599999999999999</v>
       </c>
       <c r="H4">
-        <v>0.52500000000000002</v>
+        <v>0.52600000000000002</v>
       </c>
       <c r="I4">
         <v>0.58499999999999996</v>
       </c>
       <c r="J4">
-        <v>0.59799999999999998</v>
+        <v>0.59499999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="D5">
-        <v>1E-3</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="E5">
-        <v>4.0000000000000001E-3</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="F5">
-        <v>1.4E-2</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="G5">
-        <v>1.7000000000000001E-2</v>
+        <v>6.3E-2</v>
       </c>
       <c r="H5">
-        <v>2.4E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I5">
-        <v>0.02</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="J5">
-        <v>2.1000000000000001E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.33800000000000002</v>
       </c>
       <c r="C6">
-        <v>0.55200000000000005</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="D6">
-        <v>0.59399999999999997</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="E6">
-        <v>0.64</v>
+        <v>0.625</v>
       </c>
       <c r="F6">
-        <v>0.70399999999999996</v>
+        <v>0.69</v>
       </c>
       <c r="G6">
-        <v>0.75900000000000001</v>
+        <v>0.75700000000000001</v>
       </c>
       <c r="H6">
-        <v>0.79300000000000004</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="I6">
-        <v>0.83599999999999997</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="J6">
-        <v>0.86599999999999999</v>
+        <v>0.86199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,7 +596,7 @@
         <v>0.33</v>
       </c>
       <c r="C7">
-        <v>0.44900000000000001</v>
+        <v>0.45100000000000001</v>
       </c>
       <c r="D7">
         <v>0.51500000000000001</v>
@@ -608,7 +608,7 @@
         <v>0.65700000000000003</v>
       </c>
       <c r="G7">
-        <v>0.72099999999999997</v>
+        <v>0.72399999999999998</v>
       </c>
       <c r="H7">
         <v>0.76700000000000002</v>
@@ -628,28 +628,28 @@
         <v>0.129</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="D8">
-        <v>5.5E-2</v>
+        <v>0.24099999999999999</v>
       </c>
       <c r="E8">
-        <v>0.127</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="F8">
-        <v>0.187</v>
+        <v>0.32200000000000001</v>
       </c>
       <c r="G8">
-        <v>0.247</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="H8">
-        <v>0.32100000000000001</v>
+        <v>0.42799999999999999</v>
       </c>
       <c r="I8">
-        <v>0.17499999999999999</v>
+        <v>0.47899999999999998</v>
       </c>
       <c r="J8">
-        <v>0.16800000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="C9">
-        <v>0.54700000000000004</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="D9">
-        <v>0.85899999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="E9">
-        <v>0.61899999999999999</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="F9">
-        <v>0.26200000000000001</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="G9">
-        <v>0.19400000000000001</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="H9">
-        <v>0.20399999999999999</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="I9">
-        <v>0.20699999999999999</v>
+        <v>0.185</v>
       </c>
       <c r="J9">
-        <v>0.20599999999999999</v>
+        <v>0.183</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p23.xlsx
+++ b/xlsx/Power/p23.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A5B4EE-0023-4B65-832E-9FFA63ABA364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A666C6B-1DD7-4664-AB5C-27F58CA4E253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E325A220-9FA4-40D5-B3CC-EDAAF5B26F1A}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E325A220-9FA4-40D5-B3CC-EDAAF5B26F1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,7 +398,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="B1">
         <v>0.27500000000000002</v>
@@ -407,7 +407,7 @@
         <v>0.39500000000000002</v>
       </c>
       <c r="D1">
-        <v>0.47399999999999998</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="E1">
         <v>0.56599999999999995</v>
@@ -422,42 +422,42 @@
         <v>0.73199999999999998</v>
       </c>
       <c r="I1">
-        <v>0.78</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="J1">
-        <v>0.80100000000000005</v>
+        <v>0.80200000000000005</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.17299999999999999</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="B2">
-        <v>0.313</v>
+        <v>0.315</v>
       </c>
       <c r="C2">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="D2">
         <v>0.53</v>
       </c>
       <c r="E2">
-        <v>0.60599999999999998</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="F2">
         <v>0.66300000000000003</v>
       </c>
       <c r="G2">
-        <v>0.72499999999999998</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="H2">
-        <v>0.77</v>
+        <v>0.76900000000000002</v>
       </c>
       <c r="I2">
-        <v>0.81299999999999994</v>
+        <v>0.81399999999999995</v>
       </c>
       <c r="J2">
-        <v>0.84599999999999997</v>
+        <v>0.84699999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -465,100 +465,100 @@
         <v>0.14799999999999999</v>
       </c>
       <c r="B3">
-        <v>0.23599999999999999</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="C3">
-        <v>0.32900000000000001</v>
+        <v>0.33700000000000002</v>
       </c>
       <c r="D3">
         <v>0.40200000000000002</v>
       </c>
       <c r="E3">
-        <v>0.46899999999999997</v>
+        <v>0.47299999999999998</v>
       </c>
       <c r="F3">
-        <v>0.52500000000000002</v>
+        <v>0.52600000000000002</v>
       </c>
       <c r="G3">
-        <v>0.55400000000000005</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="H3">
-        <v>0.59199999999999997</v>
+        <v>0.59399999999999997</v>
       </c>
       <c r="I3">
-        <v>0.66500000000000004</v>
+        <v>0.67700000000000005</v>
       </c>
       <c r="J3">
-        <v>0.66900000000000004</v>
+        <v>0.67700000000000005</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.14299999999999999</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="B4">
         <v>0.19800000000000001</v>
       </c>
       <c r="C4">
-        <v>0.29299999999999998</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="D4">
-        <v>0.36199999999999999</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E4">
-        <v>0.41799999999999998</v>
+        <v>0.41899999999999998</v>
       </c>
       <c r="F4">
-        <v>0.47499999999999998</v>
+        <v>0.47699999999999998</v>
       </c>
       <c r="G4">
-        <v>0.48599999999999999</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="H4">
-        <v>0.52600000000000002</v>
+        <v>0.52800000000000002</v>
       </c>
       <c r="I4">
-        <v>0.58499999999999996</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="J4">
-        <v>0.59499999999999997</v>
+        <v>0.60699999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>6.0999999999999999E-2</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="B5">
-        <v>5.3999999999999999E-2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="C5">
-        <v>6.4000000000000001E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="D5">
-        <v>6.9000000000000006E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="E5">
-        <v>7.0999999999999994E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="F5">
-        <v>6.0999999999999999E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="G5">
-        <v>6.3E-2</v>
+        <v>3.1E-2</v>
       </c>
       <c r="H5">
-        <v>7.0000000000000007E-2</v>
+        <v>0.05</v>
       </c>
       <c r="I5">
-        <v>6.8000000000000005E-2</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="J5">
-        <v>5.6000000000000001E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.186</v>
+        <v>0.184</v>
       </c>
       <c r="B6">
         <v>0.33800000000000002</v>
@@ -567,39 +567,39 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="D6">
-        <v>0.55400000000000005</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E6">
-        <v>0.625</v>
+        <v>0.624</v>
       </c>
       <c r="F6">
-        <v>0.69</v>
+        <v>0.68600000000000005</v>
       </c>
       <c r="G6">
-        <v>0.75700000000000001</v>
+        <v>0.753</v>
       </c>
       <c r="H6">
         <v>0.78900000000000003</v>
       </c>
       <c r="I6">
-        <v>0.83299999999999996</v>
+        <v>0.83199999999999996</v>
       </c>
       <c r="J6">
-        <v>0.86199999999999999</v>
+        <v>0.86399999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.182</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="B7">
-        <v>0.33</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="C7">
-        <v>0.45100000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="D7">
-        <v>0.51500000000000001</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="E7">
         <v>0.59799999999999998</v>
@@ -625,22 +625,22 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="B8">
-        <v>0.129</v>
+        <v>0.13</v>
       </c>
       <c r="C8">
         <v>0.20799999999999999</v>
       </c>
       <c r="D8">
-        <v>0.24099999999999999</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="E8">
-        <v>0.29799999999999999</v>
+        <v>0.30099999999999999</v>
       </c>
       <c r="F8">
-        <v>0.32200000000000001</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="G8">
-        <v>0.36399999999999999</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="H8">
         <v>0.42799999999999999</v>
@@ -654,34 +654,34 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>9.7000000000000003E-2</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="B9">
-        <v>9.5000000000000001E-2</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="C9">
         <v>0.28899999999999998</v>
       </c>
       <c r="D9">
-        <v>0.17</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="E9">
-        <v>0.17299999999999999</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="F9">
-        <v>0.14699999999999999</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="G9">
-        <v>0.14099999999999999</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H9">
         <v>0.16500000000000001</v>
       </c>
       <c r="I9">
-        <v>0.185</v>
+        <v>0.189</v>
       </c>
       <c r="J9">
-        <v>0.183</v>
+        <v>0.191</v>
       </c>
     </row>
   </sheetData>
